--- a/问题二/output/表2_指定日期充放电量.xlsx
+++ b/问题二/output/表2_指定日期充放电量.xlsx
@@ -471,10 +471,10 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>1666.666666666667</v>
+        <v>263.8222728497092</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>0</v>
+        <v>465.803811341863</v>
       </c>
     </row>
     <row r="4">
@@ -484,10 +484,10 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>1486.993470781892</v>
+        <v>487.9811068292019</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>3279.744666666666</v>
+        <v>5476.217951304283</v>
       </c>
     </row>
     <row r="5">
@@ -497,10 +497,10 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>5868.811199999999</v>
+        <v>3307.033598879529</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>5378.457116666666</v>
+        <v>2777.377216666667</v>
       </c>
     </row>
     <row r="6">
@@ -510,10 +510,10 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>7881.531234567901</v>
+        <v>3784.749664661231</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>3009.0403</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -523,10 +523,10 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>0</v>
+        <v>88.73522144326762</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>6083.899333333333</v>
+        <v>4258.2434875</v>
       </c>
     </row>
     <row r="8">
@@ -536,10 +536,10 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>8166.666666666666</v>
+        <v>9826.007321624218</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>2556.100666666668</v>
+        <v>1749.15968574299</v>
       </c>
     </row>
     <row r="9">
@@ -554,7 +554,7 @@
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>8550.000000000065</v>
+        <v>10405.38658971053</v>
       </c>
       <c r="C10" s="2" t="n"/>
     </row>
@@ -565,7 +565,7 @@
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>8550.000000000067</v>
+        <v>10024.76935452919</v>
       </c>
       <c r="C11" s="2" t="n"/>
     </row>
@@ -588,7 +588,7 @@
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
     <col width="21" customWidth="1" min="2" max="2"/>
-    <col width="21" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -624,10 +624,10 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>0</v>
+        <v>79.32051628874143</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>0</v>
+        <v>3049.058854313069</v>
       </c>
     </row>
     <row r="4">
@@ -637,10 +637,10 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>833.3333333333333</v>
+        <v>347.3791289170631</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>2378.821633333333</v>
+        <v>4729.459065090179</v>
       </c>
     </row>
     <row r="5">
@@ -650,10 +650,10 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>3283.330833333332</v>
+        <v>10322.21241666667</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>352.181566666666</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -663,10 +663,10 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>4131.784412757203</v>
+        <v>0</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>247.1579833333333</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -676,10 +676,10 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>0</v>
+        <v>52.01154780896854</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>5142.226416666668</v>
+        <v>5219.086287501916</v>
       </c>
     </row>
     <row r="8">
@@ -689,10 +689,10 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>307.3289917695471</v>
+        <v>9280.087058456618</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>3497.773583333333</v>
+        <v>2549.376855453602</v>
       </c>
     </row>
     <row r="9">
@@ -707,7 +707,7 @@
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>6685.464260000155</v>
+        <v>9768.77683254061</v>
       </c>
       <c r="C10" s="2" t="n"/>
     </row>
@@ -718,7 +718,7 @@
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>1476.596092592746</v>
+        <v>10567.26303124401</v>
       </c>
       <c r="C11" s="2" t="n"/>
     </row>
@@ -777,10 +777,10 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>1666.666666666667</v>
+        <v>584.747061571727</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>0</v>
+        <v>23.42372717228534</v>
       </c>
     </row>
     <row r="4">
@@ -790,10 +790,10 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>1666.666666666667</v>
+        <v>449.2586849085039</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>1200</v>
+        <v>5485.46287062497</v>
       </c>
     </row>
     <row r="5">
@@ -803,10 +803,10 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>5833.333333333333</v>
+        <v>4476.760194039398</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>8115.000000000001</v>
+        <v>1896.615716666666</v>
       </c>
     </row>
     <row r="6">
@@ -816,10 +816,10 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>8371.316133333334</v>
+        <v>4574.208139062228</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>2865.766068</v>
+        <v>554.1283936756832</v>
       </c>
     </row>
     <row r="7">
@@ -829,10 +829,10 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>0</v>
+        <v>196.4135477253607</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>6490.874750000002</v>
+        <v>5736.935062135497</v>
       </c>
     </row>
     <row r="8">
@@ -842,10 +842,10 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>8166.666666666666</v>
+        <v>9746.905589478292</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>2149.12525</v>
+        <v>2506.486455938802</v>
       </c>
     </row>
     <row r="9">
@@ -860,7 +860,7 @@
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>8550.00000000024</v>
+        <v>9986.309183431007</v>
       </c>
       <c r="C10" s="2" t="n"/>
     </row>
@@ -871,7 +871,7 @@
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>8550.00000000024</v>
+        <v>10008.38171607808</v>
       </c>
       <c r="C11" s="2" t="n"/>
     </row>
@@ -930,10 +930,10 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>1666.666666666667</v>
+        <v>721.3507946320517</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>0</v>
+        <v>144.3835559206814</v>
       </c>
     </row>
     <row r="4">
@@ -943,10 +943,10 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>833.3333333333333</v>
+        <v>1467.19585702775</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>3699.565716666666</v>
+        <v>1699.791012973842</v>
       </c>
     </row>
     <row r="5">
@@ -956,10 +956,10 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>724.7642666666673</v>
+        <v>5213.962169495377</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>2198.112433333334</v>
+        <v>6441.100865337588</v>
       </c>
     </row>
     <row r="6">
@@ -969,10 +969,10 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>3479.937379423871</v>
+        <v>6574.878218310051</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>1143.509216666666</v>
+        <v>2366.771690871053</v>
       </c>
     </row>
     <row r="7">
@@ -982,10 +982,10 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>0</v>
+        <v>36.212857248724</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>2885.265133333333</v>
+        <v>5489.221006772575</v>
       </c>
     </row>
     <row r="8">
@@ -995,10 +995,10 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>8166.666666666666</v>
+        <v>9686.270000247794</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>2119.355833333334</v>
+        <v>2928.652277995823</v>
       </c>
     </row>
     <row r="9">
@@ -1013,7 +1013,7 @@
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>8550.000000000357</v>
+        <v>10055.95958126258</v>
       </c>
       <c r="C10" s="2" t="n"/>
     </row>
@@ -1024,7 +1024,7 @@
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>8550.000000000357</v>
+        <v>10197.04203311532</v>
       </c>
       <c r="C11" s="2" t="n"/>
     </row>

--- a/问题二/output/表2_指定日期充放电量.xlsx
+++ b/问题二/output/表2_指定日期充放电量.xlsx
@@ -471,10 +471,10 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>263.8222728497092</v>
+        <v>8526.655401706055</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>465.803811341863</v>
+        <v>126.7386866251056</v>
       </c>
     </row>
     <row r="4">
@@ -484,10 +484,10 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>487.9811068292019</v>
+        <v>1657.758298881468</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>5476.217951304283</v>
+        <v>5464.323699286553</v>
       </c>
     </row>
     <row r="5">
@@ -497,7 +497,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>3307.033598879529</v>
+        <v>3306.242113856475</v>
       </c>
       <c r="C5" s="2" t="n">
         <v>2777.377216666667</v>
@@ -523,10 +523,10 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>88.73522144326762</v>
+        <v>158.9199095823867</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>4258.2434875</v>
+        <v>4040.450075</v>
       </c>
     </row>
     <row r="8">
@@ -536,10 +536,10 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>9826.007321624218</v>
+        <v>467.274067333807</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>1749.15968574299</v>
+        <v>1942.522118123344</v>
       </c>
     </row>
     <row r="9">
@@ -554,7 +554,7 @@
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>10405.38658971053</v>
+        <v>1371.545679483845</v>
       </c>
       <c r="C10" s="2" t="n"/>
     </row>
@@ -565,7 +565,7 @@
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>10024.76935452919</v>
+        <v>1536.97208356794</v>
       </c>
       <c r="C11" s="2" t="n"/>
     </row>
@@ -624,10 +624,10 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>79.32051628874143</v>
+        <v>1621.456233821742</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>3049.058854313069</v>
+        <v>366.788147977263</v>
       </c>
     </row>
     <row r="4">
@@ -637,10 +637,10 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>347.3791289170631</v>
+        <v>1193.242878591499</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>4729.459065090179</v>
+        <v>1669.329876953186</v>
       </c>
     </row>
     <row r="5">
@@ -679,7 +679,7 @@
         <v>52.01154780896854</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>5219.086287501916</v>
+        <v>5664.154500276536</v>
       </c>
     </row>
     <row r="8">
@@ -689,10 +689,10 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>9280.087058456618</v>
+        <v>479.3117024206111</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>2549.376855453602</v>
+        <v>2886.602235146302</v>
       </c>
     </row>
     <row r="9">
@@ -707,7 +707,7 @@
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>9768.77683254061</v>
+        <v>1239.132984861914</v>
       </c>
       <c r="C10" s="2" t="n"/>
     </row>
@@ -718,7 +718,7 @@
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>10567.26303124401</v>
+        <v>1777.350108070132</v>
       </c>
       <c r="C11" s="2" t="n"/>
     </row>
@@ -777,10 +777,10 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>584.747061571727</v>
+        <v>8807.251837442767</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>23.42372717228534</v>
+        <v>1.331132668584019</v>
       </c>
     </row>
     <row r="4">
@@ -790,10 +790,10 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>449.2586849085039</v>
+        <v>550.2535088555712</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>5485.46287062497</v>
+        <v>5451.508318048131</v>
       </c>
     </row>
     <row r="5">
@@ -803,7 +803,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>4476.760194039398</v>
+        <v>3723.483183034491</v>
       </c>
       <c r="C5" s="2" t="n">
         <v>1896.615716666666</v>
@@ -816,10 +816,10 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>4574.208139062228</v>
+        <v>5867.990602052249</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>554.1283936756832</v>
+        <v>670.0663484787279</v>
       </c>
     </row>
     <row r="7">
@@ -829,10 +829,10 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>196.4135477253607</v>
+        <v>195.6874765069442</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>5736.935062135497</v>
+        <v>5637.798511725341</v>
       </c>
     </row>
     <row r="8">
@@ -842,10 +842,10 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>9746.905589478292</v>
+        <v>386.2273480215271</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>2506.486455938802</v>
+        <v>2544.369144104015</v>
       </c>
     </row>
     <row r="9">
@@ -860,7 +860,7 @@
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>9986.309183431007</v>
+        <v>1819.302029953031</v>
       </c>
       <c r="C10" s="2" t="n"/>
     </row>
@@ -871,7 +871,7 @@
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>10008.38171607808</v>
+        <v>1395.229732840269</v>
       </c>
       <c r="C11" s="2" t="n"/>
     </row>
@@ -930,10 +930,10 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>721.3507946320517</v>
+        <v>9387.336031564219</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>144.3835559206814</v>
+        <v>83.29061164652501</v>
       </c>
     </row>
     <row r="4">
@@ -943,7 +943,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>1467.19585702775</v>
+        <v>2459.908981094591</v>
       </c>
       <c r="C4" s="2" t="n">
         <v>1699.791012973842</v>
@@ -972,7 +972,7 @@
         <v>6574.878218310051</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>2366.771690871053</v>
+        <v>2377.828850933572</v>
       </c>
     </row>
     <row r="7">
@@ -982,10 +982,10 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>36.212857248724</v>
+        <v>45.73262395483754</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>5489.221006772575</v>
+        <v>5486.422103395404</v>
       </c>
     </row>
     <row r="8">
@@ -995,10 +995,10 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>9686.270000247794</v>
+        <v>324.7545992474262</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>2928.652277995823</v>
+        <v>2998.368723935621</v>
       </c>
     </row>
     <row r="9">
@@ -1013,7 +1013,7 @@
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>10055.95958126258</v>
+        <v>1295.250007169972</v>
       </c>
       <c r="C10" s="2" t="n"/>
     </row>
@@ -1024,7 +1024,7 @@
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>10197.04203311532</v>
+        <v>1693.607403778102</v>
       </c>
       <c r="C11" s="2" t="n"/>
     </row>
